--- a/sql/テーブル定義.xlsx
+++ b/sql/テーブル定義.xlsx
@@ -558,10 +558,6 @@
     <rPh sb="3" eb="4">
       <t>エン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>company_statistics</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -801,6 +797,9 @@
   </si>
   <si>
     <t>REAL</t>
+  </si>
+  <si>
+    <t>equity_statistics</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1347,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1503,6 +1502,51 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" wrapText="1"/>
     </xf>
@@ -1611,47 +1655,95 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
@@ -1661,96 +1753,6 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2027,7 +2029,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2042,168 +2044,168 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" s="1" customFormat="1" ht="12.75" thickTop="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="61" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="66" t="s">
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="69" t="s">
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="AD1" s="70"/>
-      <c r="AE1" s="70"/>
-      <c r="AF1" s="70"/>
-      <c r="AG1" s="64"/>
-      <c r="AH1" s="64"/>
-      <c r="AI1" s="64"/>
-      <c r="AJ1" s="64"/>
-      <c r="AK1" s="64"/>
-      <c r="AL1" s="64"/>
-      <c r="AM1" s="64"/>
-      <c r="AN1" s="65"/>
-      <c r="AO1" s="71" t="s">
+      <c r="AD1" s="85"/>
+      <c r="AE1" s="85"/>
+      <c r="AF1" s="85"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="80"/>
+      <c r="AO1" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="75" t="s">
+      <c r="AP1" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="76"/>
-      <c r="AR1" s="77"/>
+      <c r="AQ1" s="91"/>
+      <c r="AR1" s="92"/>
     </row>
     <row r="2" spans="1:44" s="1" customFormat="1">
-      <c r="A2" s="55"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="61" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="84" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="64"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="64"/>
-      <c r="U2" s="64"/>
-      <c r="V2" s="64"/>
-      <c r="W2" s="64"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="66" t="s">
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="85" t="s">
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
+      <c r="AB2" s="83"/>
+      <c r="AC2" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="AD2" s="86"/>
-      <c r="AE2" s="86"/>
-      <c r="AF2" s="87"/>
-      <c r="AG2" s="69"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="70"/>
-      <c r="AJ2" s="70"/>
-      <c r="AK2" s="70"/>
-      <c r="AL2" s="70"/>
-      <c r="AM2" s="70"/>
-      <c r="AN2" s="74"/>
-      <c r="AO2" s="72"/>
-      <c r="AP2" s="78"/>
-      <c r="AQ2" s="79"/>
-      <c r="AR2" s="80"/>
+      <c r="AD2" s="101"/>
+      <c r="AE2" s="101"/>
+      <c r="AF2" s="102"/>
+      <c r="AG2" s="84"/>
+      <c r="AH2" s="85"/>
+      <c r="AI2" s="85"/>
+      <c r="AJ2" s="85"/>
+      <c r="AK2" s="85"/>
+      <c r="AL2" s="85"/>
+      <c r="AM2" s="85"/>
+      <c r="AN2" s="89"/>
+      <c r="AO2" s="87"/>
+      <c r="AP2" s="93"/>
+      <c r="AQ2" s="94"/>
+      <c r="AR2" s="95"/>
     </row>
     <row r="3" spans="1:44" s="1" customFormat="1" ht="12.75" thickBot="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61" t="s">
+      <c r="A3" s="73"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="84" t="s">
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="66" t="s">
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="68"/>
-      <c r="AC3" s="69"/>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="69"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="74"/>
-      <c r="AO3" s="73"/>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="82"/>
-      <c r="AR3" s="83"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="83"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="84"/>
+      <c r="AH3" s="85"/>
+      <c r="AI3" s="85"/>
+      <c r="AJ3" s="85"/>
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="85"/>
+      <c r="AM3" s="85"/>
+      <c r="AN3" s="89"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="96"/>
+      <c r="AQ3" s="97"/>
+      <c r="AR3" s="98"/>
     </row>
     <row r="4" spans="1:44" ht="7.5" customHeight="1" thickTop="1"/>
     <row r="5" spans="1:44" ht="17.25">
@@ -2213,26 +2215,26 @@
     </row>
     <row r="6" spans="1:44" ht="12" customHeight="1"/>
     <row r="7" spans="1:44">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="91" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="91" t="s">
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="93"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="65"/>
       <c r="O7" s="7" t="s">
         <v>56</v>
       </c>
@@ -2258,1401 +2260,1401 @@
       <c r="AI7" s="8"/>
       <c r="AJ7" s="8"/>
       <c r="AK7" s="9"/>
-      <c r="AL7" s="91" t="s">
+      <c r="AL7" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="AM7" s="92"/>
-      <c r="AN7" s="92"/>
-      <c r="AO7" s="92"/>
-      <c r="AP7" s="92"/>
-      <c r="AQ7" s="92"/>
-      <c r="AR7" s="93"/>
+      <c r="AM7" s="64"/>
+      <c r="AN7" s="64"/>
+      <c r="AO7" s="64"/>
+      <c r="AP7" s="64"/>
+      <c r="AQ7" s="64"/>
+      <c r="AR7" s="65"/>
     </row>
     <row r="8" spans="1:44">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="97">
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="66">
         <v>44683</v>
       </c>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="99"/>
-      <c r="O8" s="100" t="s">
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="98"/>
-      <c r="U8" s="98"/>
-      <c r="V8" s="98"/>
-      <c r="W8" s="98"/>
-      <c r="X8" s="98"/>
-      <c r="Y8" s="98"/>
-      <c r="Z8" s="98"/>
-      <c r="AA8" s="98"/>
-      <c r="AB8" s="98"/>
-      <c r="AC8" s="98"/>
-      <c r="AD8" s="98"/>
-      <c r="AE8" s="98"/>
-      <c r="AF8" s="98"/>
-      <c r="AG8" s="98"/>
-      <c r="AH8" s="98"/>
-      <c r="AI8" s="98"/>
-      <c r="AJ8" s="98"/>
-      <c r="AK8" s="99"/>
-      <c r="AL8" s="100"/>
-      <c r="AM8" s="98"/>
-      <c r="AN8" s="98"/>
-      <c r="AO8" s="98"/>
-      <c r="AP8" s="98"/>
-      <c r="AQ8" s="98"/>
-      <c r="AR8" s="99"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="57"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="57"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="57"/>
+      <c r="AA8" s="57"/>
+      <c r="AB8" s="57"/>
+      <c r="AC8" s="57"/>
+      <c r="AD8" s="57"/>
+      <c r="AE8" s="57"/>
+      <c r="AF8" s="57"/>
+      <c r="AG8" s="57"/>
+      <c r="AH8" s="57"/>
+      <c r="AI8" s="57"/>
+      <c r="AJ8" s="57"/>
+      <c r="AK8" s="58"/>
+      <c r="AL8" s="56"/>
+      <c r="AM8" s="57"/>
+      <c r="AN8" s="57"/>
+      <c r="AO8" s="57"/>
+      <c r="AP8" s="57"/>
+      <c r="AQ8" s="57"/>
+      <c r="AR8" s="58"/>
     </row>
     <row r="9" spans="1:44">
-      <c r="A9" s="94"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="101"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="98"/>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="98"/>
-      <c r="W9" s="98"/>
-      <c r="X9" s="98"/>
-      <c r="Y9" s="98"/>
-      <c r="Z9" s="98"/>
-      <c r="AA9" s="98"/>
-      <c r="AB9" s="98"/>
-      <c r="AC9" s="98"/>
-      <c r="AD9" s="98"/>
-      <c r="AE9" s="98"/>
-      <c r="AF9" s="98"/>
-      <c r="AG9" s="98"/>
-      <c r="AH9" s="98"/>
-      <c r="AI9" s="98"/>
-      <c r="AJ9" s="98"/>
-      <c r="AK9" s="99"/>
-      <c r="AL9" s="100"/>
-      <c r="AM9" s="98"/>
-      <c r="AN9" s="98"/>
-      <c r="AO9" s="98"/>
-      <c r="AP9" s="98"/>
-      <c r="AQ9" s="98"/>
-      <c r="AR9" s="99"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="59"/>
+      <c r="P9" s="57"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="57"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="57"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="57"/>
+      <c r="Y9" s="57"/>
+      <c r="Z9" s="57"/>
+      <c r="AA9" s="57"/>
+      <c r="AB9" s="57"/>
+      <c r="AC9" s="57"/>
+      <c r="AD9" s="57"/>
+      <c r="AE9" s="57"/>
+      <c r="AF9" s="57"/>
+      <c r="AG9" s="57"/>
+      <c r="AH9" s="57"/>
+      <c r="AI9" s="57"/>
+      <c r="AJ9" s="57"/>
+      <c r="AK9" s="58"/>
+      <c r="AL9" s="56"/>
+      <c r="AM9" s="57"/>
+      <c r="AN9" s="57"/>
+      <c r="AO9" s="57"/>
+      <c r="AP9" s="57"/>
+      <c r="AQ9" s="57"/>
+      <c r="AR9" s="58"/>
     </row>
     <row r="10" spans="1:44">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="98"/>
-      <c r="M10" s="98"/>
-      <c r="N10" s="99"/>
-      <c r="O10" s="101"/>
-      <c r="P10" s="98"/>
-      <c r="Q10" s="98"/>
-      <c r="R10" s="98"/>
-      <c r="S10" s="98"/>
-      <c r="T10" s="98"/>
-      <c r="U10" s="98"/>
-      <c r="V10" s="98"/>
-      <c r="W10" s="98"/>
-      <c r="X10" s="98"/>
-      <c r="Y10" s="98"/>
-      <c r="Z10" s="98"/>
-      <c r="AA10" s="98"/>
-      <c r="AB10" s="98"/>
-      <c r="AC10" s="98"/>
-      <c r="AD10" s="98"/>
-      <c r="AE10" s="98"/>
-      <c r="AF10" s="98"/>
-      <c r="AG10" s="98"/>
-      <c r="AH10" s="98"/>
-      <c r="AI10" s="98"/>
-      <c r="AJ10" s="98"/>
-      <c r="AK10" s="99"/>
-      <c r="AL10" s="100"/>
-      <c r="AM10" s="98"/>
-      <c r="AN10" s="98"/>
-      <c r="AO10" s="98"/>
-      <c r="AP10" s="98"/>
-      <c r="AQ10" s="98"/>
-      <c r="AR10" s="99"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="58"/>
+      <c r="O10" s="59"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="57"/>
+      <c r="S10" s="57"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="57"/>
+      <c r="W10" s="57"/>
+      <c r="X10" s="57"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="57"/>
+      <c r="AA10" s="57"/>
+      <c r="AB10" s="57"/>
+      <c r="AC10" s="57"/>
+      <c r="AD10" s="57"/>
+      <c r="AE10" s="57"/>
+      <c r="AF10" s="57"/>
+      <c r="AG10" s="57"/>
+      <c r="AH10" s="57"/>
+      <c r="AI10" s="57"/>
+      <c r="AJ10" s="57"/>
+      <c r="AK10" s="58"/>
+      <c r="AL10" s="56"/>
+      <c r="AM10" s="57"/>
+      <c r="AN10" s="57"/>
+      <c r="AO10" s="57"/>
+      <c r="AP10" s="57"/>
+      <c r="AQ10" s="57"/>
+      <c r="AR10" s="58"/>
     </row>
     <row r="11" spans="1:44">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="100"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
-      <c r="S11" s="98"/>
-      <c r="T11" s="98"/>
-      <c r="U11" s="98"/>
-      <c r="V11" s="98"/>
-      <c r="W11" s="98"/>
-      <c r="X11" s="98"/>
-      <c r="Y11" s="98"/>
-      <c r="Z11" s="98"/>
-      <c r="AA11" s="98"/>
-      <c r="AB11" s="98"/>
-      <c r="AC11" s="98"/>
-      <c r="AD11" s="98"/>
-      <c r="AE11" s="98"/>
-      <c r="AF11" s="98"/>
-      <c r="AG11" s="98"/>
-      <c r="AH11" s="98"/>
-      <c r="AI11" s="98"/>
-      <c r="AJ11" s="98"/>
-      <c r="AK11" s="99"/>
-      <c r="AL11" s="100"/>
-      <c r="AM11" s="98"/>
-      <c r="AN11" s="98"/>
-      <c r="AO11" s="98"/>
-      <c r="AP11" s="98"/>
-      <c r="AQ11" s="98"/>
-      <c r="AR11" s="99"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="57"/>
+      <c r="X11" s="57"/>
+      <c r="Y11" s="57"/>
+      <c r="Z11" s="57"/>
+      <c r="AA11" s="57"/>
+      <c r="AB11" s="57"/>
+      <c r="AC11" s="57"/>
+      <c r="AD11" s="57"/>
+      <c r="AE11" s="57"/>
+      <c r="AF11" s="57"/>
+      <c r="AG11" s="57"/>
+      <c r="AH11" s="57"/>
+      <c r="AI11" s="57"/>
+      <c r="AJ11" s="57"/>
+      <c r="AK11" s="58"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="57"/>
+      <c r="AN11" s="57"/>
+      <c r="AO11" s="57"/>
+      <c r="AP11" s="57"/>
+      <c r="AQ11" s="57"/>
+      <c r="AR11" s="58"/>
     </row>
     <row r="12" spans="1:44">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="100"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="98"/>
-      <c r="AB12" s="98"/>
-      <c r="AC12" s="98"/>
-      <c r="AD12" s="98"/>
-      <c r="AE12" s="98"/>
-      <c r="AF12" s="98"/>
-      <c r="AG12" s="98"/>
-      <c r="AH12" s="98"/>
-      <c r="AI12" s="98"/>
-      <c r="AJ12" s="98"/>
-      <c r="AK12" s="99"/>
-      <c r="AL12" s="100"/>
-      <c r="AM12" s="98"/>
-      <c r="AN12" s="98"/>
-      <c r="AO12" s="98"/>
-      <c r="AP12" s="98"/>
-      <c r="AQ12" s="98"/>
-      <c r="AR12" s="99"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="57"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="57"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="57"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="57"/>
+      <c r="AG12" s="57"/>
+      <c r="AH12" s="57"/>
+      <c r="AI12" s="57"/>
+      <c r="AJ12" s="57"/>
+      <c r="AK12" s="58"/>
+      <c r="AL12" s="56"/>
+      <c r="AM12" s="57"/>
+      <c r="AN12" s="57"/>
+      <c r="AO12" s="57"/>
+      <c r="AP12" s="57"/>
+      <c r="AQ12" s="57"/>
+      <c r="AR12" s="58"/>
     </row>
     <row r="13" spans="1:44">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="98"/>
-      <c r="Q13" s="98"/>
-      <c r="R13" s="98"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="98"/>
-      <c r="U13" s="98"/>
-      <c r="V13" s="98"/>
-      <c r="W13" s="98"/>
-      <c r="X13" s="98"/>
-      <c r="Y13" s="98"/>
-      <c r="Z13" s="98"/>
-      <c r="AA13" s="98"/>
-      <c r="AB13" s="98"/>
-      <c r="AC13" s="98"/>
-      <c r="AD13" s="98"/>
-      <c r="AE13" s="98"/>
-      <c r="AF13" s="98"/>
-      <c r="AG13" s="98"/>
-      <c r="AH13" s="98"/>
-      <c r="AI13" s="98"/>
-      <c r="AJ13" s="98"/>
-      <c r="AK13" s="99"/>
-      <c r="AL13" s="100"/>
-      <c r="AM13" s="98"/>
-      <c r="AN13" s="98"/>
-      <c r="AO13" s="98"/>
-      <c r="AP13" s="98"/>
-      <c r="AQ13" s="98"/>
-      <c r="AR13" s="99"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="57"/>
+      <c r="Y13" s="57"/>
+      <c r="Z13" s="57"/>
+      <c r="AA13" s="57"/>
+      <c r="AB13" s="57"/>
+      <c r="AC13" s="57"/>
+      <c r="AD13" s="57"/>
+      <c r="AE13" s="57"/>
+      <c r="AF13" s="57"/>
+      <c r="AG13" s="57"/>
+      <c r="AH13" s="57"/>
+      <c r="AI13" s="57"/>
+      <c r="AJ13" s="57"/>
+      <c r="AK13" s="58"/>
+      <c r="AL13" s="56"/>
+      <c r="AM13" s="57"/>
+      <c r="AN13" s="57"/>
+      <c r="AO13" s="57"/>
+      <c r="AP13" s="57"/>
+      <c r="AQ13" s="57"/>
+      <c r="AR13" s="58"/>
     </row>
     <row r="14" spans="1:44">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-      <c r="N14" s="99"/>
-      <c r="O14" s="100"/>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="98"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="98"/>
-      <c r="U14" s="98"/>
-      <c r="V14" s="98"/>
-      <c r="W14" s="98"/>
-      <c r="X14" s="98"/>
-      <c r="Y14" s="98"/>
-      <c r="Z14" s="98"/>
-      <c r="AA14" s="98"/>
-      <c r="AB14" s="98"/>
-      <c r="AC14" s="98"/>
-      <c r="AD14" s="98"/>
-      <c r="AE14" s="98"/>
-      <c r="AF14" s="98"/>
-      <c r="AG14" s="98"/>
-      <c r="AH14" s="98"/>
-      <c r="AI14" s="98"/>
-      <c r="AJ14" s="98"/>
-      <c r="AK14" s="99"/>
-      <c r="AL14" s="100"/>
-      <c r="AM14" s="98"/>
-      <c r="AN14" s="98"/>
-      <c r="AO14" s="98"/>
-      <c r="AP14" s="98"/>
-      <c r="AQ14" s="98"/>
-      <c r="AR14" s="99"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="57"/>
+      <c r="Y14" s="57"/>
+      <c r="Z14" s="57"/>
+      <c r="AA14" s="57"/>
+      <c r="AB14" s="57"/>
+      <c r="AC14" s="57"/>
+      <c r="AD14" s="57"/>
+      <c r="AE14" s="57"/>
+      <c r="AF14" s="57"/>
+      <c r="AG14" s="57"/>
+      <c r="AH14" s="57"/>
+      <c r="AI14" s="57"/>
+      <c r="AJ14" s="57"/>
+      <c r="AK14" s="58"/>
+      <c r="AL14" s="56"/>
+      <c r="AM14" s="57"/>
+      <c r="AN14" s="57"/>
+      <c r="AO14" s="57"/>
+      <c r="AP14" s="57"/>
+      <c r="AQ14" s="57"/>
+      <c r="AR14" s="58"/>
     </row>
     <row r="15" spans="1:44">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="98"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="100"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="98"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="98"/>
-      <c r="T15" s="98"/>
-      <c r="U15" s="98"/>
-      <c r="V15" s="98"/>
-      <c r="W15" s="98"/>
-      <c r="X15" s="98"/>
-      <c r="Y15" s="98"/>
-      <c r="Z15" s="98"/>
-      <c r="AA15" s="98"/>
-      <c r="AB15" s="98"/>
-      <c r="AC15" s="98"/>
-      <c r="AD15" s="98"/>
-      <c r="AE15" s="98"/>
-      <c r="AF15" s="98"/>
-      <c r="AG15" s="98"/>
-      <c r="AH15" s="98"/>
-      <c r="AI15" s="98"/>
-      <c r="AJ15" s="98"/>
-      <c r="AK15" s="99"/>
-      <c r="AL15" s="100"/>
-      <c r="AM15" s="98"/>
-      <c r="AN15" s="98"/>
-      <c r="AO15" s="98"/>
-      <c r="AP15" s="98"/>
-      <c r="AQ15" s="98"/>
-      <c r="AR15" s="99"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="57"/>
+      <c r="V15" s="57"/>
+      <c r="W15" s="57"/>
+      <c r="X15" s="57"/>
+      <c r="Y15" s="57"/>
+      <c r="Z15" s="57"/>
+      <c r="AA15" s="57"/>
+      <c r="AB15" s="57"/>
+      <c r="AC15" s="57"/>
+      <c r="AD15" s="57"/>
+      <c r="AE15" s="57"/>
+      <c r="AF15" s="57"/>
+      <c r="AG15" s="57"/>
+      <c r="AH15" s="57"/>
+      <c r="AI15" s="57"/>
+      <c r="AJ15" s="57"/>
+      <c r="AK15" s="58"/>
+      <c r="AL15" s="56"/>
+      <c r="AM15" s="57"/>
+      <c r="AN15" s="57"/>
+      <c r="AO15" s="57"/>
+      <c r="AP15" s="57"/>
+      <c r="AQ15" s="57"/>
+      <c r="AR15" s="58"/>
     </row>
     <row r="16" spans="1:44">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="99"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98"/>
-      <c r="N16" s="99"/>
-      <c r="O16" s="100"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="98"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="98"/>
-      <c r="V16" s="98"/>
-      <c r="W16" s="98"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="98"/>
-      <c r="Z16" s="98"/>
-      <c r="AA16" s="98"/>
-      <c r="AB16" s="98"/>
-      <c r="AC16" s="98"/>
-      <c r="AD16" s="98"/>
-      <c r="AE16" s="98"/>
-      <c r="AF16" s="98"/>
-      <c r="AG16" s="98"/>
-      <c r="AH16" s="98"/>
-      <c r="AI16" s="98"/>
-      <c r="AJ16" s="98"/>
-      <c r="AK16" s="99"/>
-      <c r="AL16" s="100"/>
-      <c r="AM16" s="98"/>
-      <c r="AN16" s="98"/>
-      <c r="AO16" s="98"/>
-      <c r="AP16" s="98"/>
-      <c r="AQ16" s="98"/>
-      <c r="AR16" s="99"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="57"/>
+      <c r="W16" s="57"/>
+      <c r="X16" s="57"/>
+      <c r="Y16" s="57"/>
+      <c r="Z16" s="57"/>
+      <c r="AA16" s="57"/>
+      <c r="AB16" s="57"/>
+      <c r="AC16" s="57"/>
+      <c r="AD16" s="57"/>
+      <c r="AE16" s="57"/>
+      <c r="AF16" s="57"/>
+      <c r="AG16" s="57"/>
+      <c r="AH16" s="57"/>
+      <c r="AI16" s="57"/>
+      <c r="AJ16" s="57"/>
+      <c r="AK16" s="58"/>
+      <c r="AL16" s="56"/>
+      <c r="AM16" s="57"/>
+      <c r="AN16" s="57"/>
+      <c r="AO16" s="57"/>
+      <c r="AP16" s="57"/>
+      <c r="AQ16" s="57"/>
+      <c r="AR16" s="58"/>
     </row>
     <row r="17" spans="1:44">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
-      <c r="AA17" s="98"/>
-      <c r="AB17" s="98"/>
-      <c r="AC17" s="98"/>
-      <c r="AD17" s="98"/>
-      <c r="AE17" s="98"/>
-      <c r="AF17" s="98"/>
-      <c r="AG17" s="98"/>
-      <c r="AH17" s="98"/>
-      <c r="AI17" s="98"/>
-      <c r="AJ17" s="98"/>
-      <c r="AK17" s="99"/>
-      <c r="AL17" s="100"/>
-      <c r="AM17" s="98"/>
-      <c r="AN17" s="98"/>
-      <c r="AO17" s="98"/>
-      <c r="AP17" s="98"/>
-      <c r="AQ17" s="98"/>
-      <c r="AR17" s="99"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="56"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="57"/>
+      <c r="W17" s="57"/>
+      <c r="X17" s="57"/>
+      <c r="Y17" s="57"/>
+      <c r="Z17" s="57"/>
+      <c r="AA17" s="57"/>
+      <c r="AB17" s="57"/>
+      <c r="AC17" s="57"/>
+      <c r="AD17" s="57"/>
+      <c r="AE17" s="57"/>
+      <c r="AF17" s="57"/>
+      <c r="AG17" s="57"/>
+      <c r="AH17" s="57"/>
+      <c r="AI17" s="57"/>
+      <c r="AJ17" s="57"/>
+      <c r="AK17" s="58"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="57"/>
+      <c r="AN17" s="57"/>
+      <c r="AO17" s="57"/>
+      <c r="AP17" s="57"/>
+      <c r="AQ17" s="57"/>
+      <c r="AR17" s="58"/>
     </row>
     <row r="18" spans="1:44">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="99"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="98"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="98"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="98"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="98"/>
-      <c r="Z18" s="98"/>
-      <c r="AA18" s="98"/>
-      <c r="AB18" s="98"/>
-      <c r="AC18" s="98"/>
-      <c r="AD18" s="98"/>
-      <c r="AE18" s="98"/>
-      <c r="AF18" s="98"/>
-      <c r="AG18" s="98"/>
-      <c r="AH18" s="98"/>
-      <c r="AI18" s="98"/>
-      <c r="AJ18" s="98"/>
-      <c r="AK18" s="99"/>
-      <c r="AL18" s="100"/>
-      <c r="AM18" s="98"/>
-      <c r="AN18" s="98"/>
-      <c r="AO18" s="98"/>
-      <c r="AP18" s="98"/>
-      <c r="AQ18" s="98"/>
-      <c r="AR18" s="99"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="57"/>
+      <c r="W18" s="57"/>
+      <c r="X18" s="57"/>
+      <c r="Y18" s="57"/>
+      <c r="Z18" s="57"/>
+      <c r="AA18" s="57"/>
+      <c r="AB18" s="57"/>
+      <c r="AC18" s="57"/>
+      <c r="AD18" s="57"/>
+      <c r="AE18" s="57"/>
+      <c r="AF18" s="57"/>
+      <c r="AG18" s="57"/>
+      <c r="AH18" s="57"/>
+      <c r="AI18" s="57"/>
+      <c r="AJ18" s="57"/>
+      <c r="AK18" s="58"/>
+      <c r="AL18" s="56"/>
+      <c r="AM18" s="57"/>
+      <c r="AN18" s="57"/>
+      <c r="AO18" s="57"/>
+      <c r="AP18" s="57"/>
+      <c r="AQ18" s="57"/>
+      <c r="AR18" s="58"/>
     </row>
     <row r="19" spans="1:44">
-      <c r="A19" s="94"/>
-      <c r="B19" s="95"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="98"/>
-      <c r="T19" s="98"/>
-      <c r="U19" s="98"/>
-      <c r="V19" s="98"/>
-      <c r="W19" s="98"/>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="98"/>
-      <c r="Z19" s="98"/>
-      <c r="AA19" s="98"/>
-      <c r="AB19" s="98"/>
-      <c r="AC19" s="98"/>
-      <c r="AD19" s="98"/>
-      <c r="AE19" s="98"/>
-      <c r="AF19" s="98"/>
-      <c r="AG19" s="98"/>
-      <c r="AH19" s="98"/>
-      <c r="AI19" s="98"/>
-      <c r="AJ19" s="98"/>
-      <c r="AK19" s="99"/>
-      <c r="AL19" s="100"/>
-      <c r="AM19" s="98"/>
-      <c r="AN19" s="98"/>
-      <c r="AO19" s="98"/>
-      <c r="AP19" s="98"/>
-      <c r="AQ19" s="98"/>
-      <c r="AR19" s="99"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="56"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="58"/>
+      <c r="AL19" s="56"/>
+      <c r="AM19" s="57"/>
+      <c r="AN19" s="57"/>
+      <c r="AO19" s="57"/>
+      <c r="AP19" s="57"/>
+      <c r="AQ19" s="57"/>
+      <c r="AR19" s="58"/>
     </row>
     <row r="20" spans="1:44">
-      <c r="A20" s="94"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="99"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-      <c r="N20" s="99"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="98"/>
-      <c r="T20" s="98"/>
-      <c r="U20" s="98"/>
-      <c r="V20" s="98"/>
-      <c r="W20" s="98"/>
-      <c r="X20" s="98"/>
-      <c r="Y20" s="98"/>
-      <c r="Z20" s="98"/>
-      <c r="AA20" s="98"/>
-      <c r="AB20" s="98"/>
-      <c r="AC20" s="98"/>
-      <c r="AD20" s="98"/>
-      <c r="AE20" s="98"/>
-      <c r="AF20" s="98"/>
-      <c r="AG20" s="98"/>
-      <c r="AH20" s="98"/>
-      <c r="AI20" s="98"/>
-      <c r="AJ20" s="98"/>
-      <c r="AK20" s="99"/>
-      <c r="AL20" s="100"/>
-      <c r="AM20" s="98"/>
-      <c r="AN20" s="98"/>
-      <c r="AO20" s="98"/>
-      <c r="AP20" s="98"/>
-      <c r="AQ20" s="98"/>
-      <c r="AR20" s="99"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="56"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="57"/>
+      <c r="Y20" s="57"/>
+      <c r="Z20" s="57"/>
+      <c r="AA20" s="57"/>
+      <c r="AB20" s="57"/>
+      <c r="AC20" s="57"/>
+      <c r="AD20" s="57"/>
+      <c r="AE20" s="57"/>
+      <c r="AF20" s="57"/>
+      <c r="AG20" s="57"/>
+      <c r="AH20" s="57"/>
+      <c r="AI20" s="57"/>
+      <c r="AJ20" s="57"/>
+      <c r="AK20" s="58"/>
+      <c r="AL20" s="56"/>
+      <c r="AM20" s="57"/>
+      <c r="AN20" s="57"/>
+      <c r="AO20" s="57"/>
+      <c r="AP20" s="57"/>
+      <c r="AQ20" s="57"/>
+      <c r="AR20" s="58"/>
     </row>
     <row r="21" spans="1:44">
-      <c r="A21" s="94"/>
-      <c r="B21" s="95"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="100"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="98"/>
-      <c r="T21" s="98"/>
-      <c r="U21" s="98"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="98"/>
-      <c r="X21" s="98"/>
-      <c r="Y21" s="98"/>
-      <c r="Z21" s="98"/>
-      <c r="AA21" s="98"/>
-      <c r="AB21" s="98"/>
-      <c r="AC21" s="98"/>
-      <c r="AD21" s="98"/>
-      <c r="AE21" s="98"/>
-      <c r="AF21" s="98"/>
-      <c r="AG21" s="98"/>
-      <c r="AH21" s="98"/>
-      <c r="AI21" s="98"/>
-      <c r="AJ21" s="98"/>
-      <c r="AK21" s="99"/>
-      <c r="AL21" s="100"/>
-      <c r="AM21" s="98"/>
-      <c r="AN21" s="98"/>
-      <c r="AO21" s="98"/>
-      <c r="AP21" s="98"/>
-      <c r="AQ21" s="98"/>
-      <c r="AR21" s="99"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+      <c r="V21" s="57"/>
+      <c r="W21" s="57"/>
+      <c r="X21" s="57"/>
+      <c r="Y21" s="57"/>
+      <c r="Z21" s="57"/>
+      <c r="AA21" s="57"/>
+      <c r="AB21" s="57"/>
+      <c r="AC21" s="57"/>
+      <c r="AD21" s="57"/>
+      <c r="AE21" s="57"/>
+      <c r="AF21" s="57"/>
+      <c r="AG21" s="57"/>
+      <c r="AH21" s="57"/>
+      <c r="AI21" s="57"/>
+      <c r="AJ21" s="57"/>
+      <c r="AK21" s="58"/>
+      <c r="AL21" s="56"/>
+      <c r="AM21" s="57"/>
+      <c r="AN21" s="57"/>
+      <c r="AO21" s="57"/>
+      <c r="AP21" s="57"/>
+      <c r="AQ21" s="57"/>
+      <c r="AR21" s="58"/>
     </row>
     <row r="22" spans="1:44">
-      <c r="A22" s="94"/>
-      <c r="B22" s="95"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="99"/>
-      <c r="H22" s="100"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="99"/>
-      <c r="O22" s="100"/>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="98"/>
-      <c r="W22" s="98"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="98"/>
-      <c r="Z22" s="98"/>
-      <c r="AA22" s="98"/>
-      <c r="AB22" s="98"/>
-      <c r="AC22" s="98"/>
-      <c r="AD22" s="98"/>
-      <c r="AE22" s="98"/>
-      <c r="AF22" s="98"/>
-      <c r="AG22" s="98"/>
-      <c r="AH22" s="98"/>
-      <c r="AI22" s="98"/>
-      <c r="AJ22" s="98"/>
-      <c r="AK22" s="99"/>
-      <c r="AL22" s="100"/>
-      <c r="AM22" s="98"/>
-      <c r="AN22" s="98"/>
-      <c r="AO22" s="98"/>
-      <c r="AP22" s="98"/>
-      <c r="AQ22" s="98"/>
-      <c r="AR22" s="99"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="57"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="57"/>
+      <c r="V22" s="57"/>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="57"/>
+      <c r="AG22" s="57"/>
+      <c r="AH22" s="57"/>
+      <c r="AI22" s="57"/>
+      <c r="AJ22" s="57"/>
+      <c r="AK22" s="58"/>
+      <c r="AL22" s="56"/>
+      <c r="AM22" s="57"/>
+      <c r="AN22" s="57"/>
+      <c r="AO22" s="57"/>
+      <c r="AP22" s="57"/>
+      <c r="AQ22" s="57"/>
+      <c r="AR22" s="58"/>
     </row>
     <row r="23" spans="1:44">
-      <c r="A23" s="94"/>
-      <c r="B23" s="95"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="99"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-      <c r="N23" s="99"/>
-      <c r="O23" s="100"/>
-      <c r="P23" s="98"/>
-      <c r="Q23" s="98"/>
-      <c r="R23" s="98"/>
-      <c r="S23" s="98"/>
-      <c r="T23" s="98"/>
-      <c r="U23" s="98"/>
-      <c r="V23" s="98"/>
-      <c r="W23" s="98"/>
-      <c r="X23" s="98"/>
-      <c r="Y23" s="98"/>
-      <c r="Z23" s="98"/>
-      <c r="AA23" s="98"/>
-      <c r="AB23" s="98"/>
-      <c r="AC23" s="98"/>
-      <c r="AD23" s="98"/>
-      <c r="AE23" s="98"/>
-      <c r="AF23" s="98"/>
-      <c r="AG23" s="98"/>
-      <c r="AH23" s="98"/>
-      <c r="AI23" s="98"/>
-      <c r="AJ23" s="98"/>
-      <c r="AK23" s="99"/>
-      <c r="AL23" s="100"/>
-      <c r="AM23" s="98"/>
-      <c r="AN23" s="98"/>
-      <c r="AO23" s="98"/>
-      <c r="AP23" s="98"/>
-      <c r="AQ23" s="98"/>
-      <c r="AR23" s="99"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="57"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="57"/>
+      <c r="V23" s="57"/>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="57"/>
+      <c r="AG23" s="57"/>
+      <c r="AH23" s="57"/>
+      <c r="AI23" s="57"/>
+      <c r="AJ23" s="57"/>
+      <c r="AK23" s="58"/>
+      <c r="AL23" s="56"/>
+      <c r="AM23" s="57"/>
+      <c r="AN23" s="57"/>
+      <c r="AO23" s="57"/>
+      <c r="AP23" s="57"/>
+      <c r="AQ23" s="57"/>
+      <c r="AR23" s="58"/>
     </row>
     <row r="24" spans="1:44">
-      <c r="A24" s="94"/>
-      <c r="B24" s="95"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="98"/>
-      <c r="N24" s="99"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="98"/>
-      <c r="Q24" s="98"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="98"/>
-      <c r="T24" s="98"/>
-      <c r="U24" s="98"/>
-      <c r="V24" s="98"/>
-      <c r="W24" s="98"/>
-      <c r="X24" s="98"/>
-      <c r="Y24" s="98"/>
-      <c r="Z24" s="98"/>
-      <c r="AA24" s="98"/>
-      <c r="AB24" s="98"/>
-      <c r="AC24" s="98"/>
-      <c r="AD24" s="98"/>
-      <c r="AE24" s="98"/>
-      <c r="AF24" s="98"/>
-      <c r="AG24" s="98"/>
-      <c r="AH24" s="98"/>
-      <c r="AI24" s="98"/>
-      <c r="AJ24" s="98"/>
-      <c r="AK24" s="99"/>
-      <c r="AL24" s="100"/>
-      <c r="AM24" s="98"/>
-      <c r="AN24" s="98"/>
-      <c r="AO24" s="98"/>
-      <c r="AP24" s="98"/>
-      <c r="AQ24" s="98"/>
-      <c r="AR24" s="99"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="57"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="57"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="57"/>
+      <c r="V24" s="57"/>
+      <c r="W24" s="57"/>
+      <c r="X24" s="57"/>
+      <c r="Y24" s="57"/>
+      <c r="Z24" s="57"/>
+      <c r="AA24" s="57"/>
+      <c r="AB24" s="57"/>
+      <c r="AC24" s="57"/>
+      <c r="AD24" s="57"/>
+      <c r="AE24" s="57"/>
+      <c r="AF24" s="57"/>
+      <c r="AG24" s="57"/>
+      <c r="AH24" s="57"/>
+      <c r="AI24" s="57"/>
+      <c r="AJ24" s="57"/>
+      <c r="AK24" s="58"/>
+      <c r="AL24" s="56"/>
+      <c r="AM24" s="57"/>
+      <c r="AN24" s="57"/>
+      <c r="AO24" s="57"/>
+      <c r="AP24" s="57"/>
+      <c r="AQ24" s="57"/>
+      <c r="AR24" s="58"/>
     </row>
     <row r="25" spans="1:44">
-      <c r="A25" s="94"/>
-      <c r="B25" s="95"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="98"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="98"/>
-      <c r="Q25" s="98"/>
-      <c r="R25" s="98"/>
-      <c r="S25" s="98"/>
-      <c r="T25" s="98"/>
-      <c r="U25" s="98"/>
-      <c r="V25" s="98"/>
-      <c r="W25" s="98"/>
-      <c r="X25" s="98"/>
-      <c r="Y25" s="98"/>
-      <c r="Z25" s="98"/>
-      <c r="AA25" s="98"/>
-      <c r="AB25" s="98"/>
-      <c r="AC25" s="98"/>
-      <c r="AD25" s="98"/>
-      <c r="AE25" s="98"/>
-      <c r="AF25" s="98"/>
-      <c r="AG25" s="98"/>
-      <c r="AH25" s="98"/>
-      <c r="AI25" s="98"/>
-      <c r="AJ25" s="98"/>
-      <c r="AK25" s="99"/>
-      <c r="AL25" s="100"/>
-      <c r="AM25" s="98"/>
-      <c r="AN25" s="98"/>
-      <c r="AO25" s="98"/>
-      <c r="AP25" s="98"/>
-      <c r="AQ25" s="98"/>
-      <c r="AR25" s="99"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="57"/>
+      <c r="V25" s="57"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="57"/>
+      <c r="Y25" s="57"/>
+      <c r="Z25" s="57"/>
+      <c r="AA25" s="57"/>
+      <c r="AB25" s="57"/>
+      <c r="AC25" s="57"/>
+      <c r="AD25" s="57"/>
+      <c r="AE25" s="57"/>
+      <c r="AF25" s="57"/>
+      <c r="AG25" s="57"/>
+      <c r="AH25" s="57"/>
+      <c r="AI25" s="57"/>
+      <c r="AJ25" s="57"/>
+      <c r="AK25" s="58"/>
+      <c r="AL25" s="56"/>
+      <c r="AM25" s="57"/>
+      <c r="AN25" s="57"/>
+      <c r="AO25" s="57"/>
+      <c r="AP25" s="57"/>
+      <c r="AQ25" s="57"/>
+      <c r="AR25" s="58"/>
     </row>
     <row r="26" spans="1:44">
-      <c r="A26" s="94"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="98"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="98"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="100"/>
-      <c r="P26" s="98"/>
-      <c r="Q26" s="98"/>
-      <c r="R26" s="98"/>
-      <c r="S26" s="98"/>
-      <c r="T26" s="98"/>
-      <c r="U26" s="98"/>
-      <c r="V26" s="98"/>
-      <c r="W26" s="98"/>
-      <c r="X26" s="98"/>
-      <c r="Y26" s="98"/>
-      <c r="Z26" s="98"/>
-      <c r="AA26" s="98"/>
-      <c r="AB26" s="98"/>
-      <c r="AC26" s="98"/>
-      <c r="AD26" s="98"/>
-      <c r="AE26" s="98"/>
-      <c r="AF26" s="98"/>
-      <c r="AG26" s="98"/>
-      <c r="AH26" s="98"/>
-      <c r="AI26" s="98"/>
-      <c r="AJ26" s="98"/>
-      <c r="AK26" s="99"/>
-      <c r="AL26" s="100"/>
-      <c r="AM26" s="98"/>
-      <c r="AN26" s="98"/>
-      <c r="AO26" s="98"/>
-      <c r="AP26" s="98"/>
-      <c r="AQ26" s="98"/>
-      <c r="AR26" s="99"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="57"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="57"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+      <c r="AF26" s="57"/>
+      <c r="AG26" s="57"/>
+      <c r="AH26" s="57"/>
+      <c r="AI26" s="57"/>
+      <c r="AJ26" s="57"/>
+      <c r="AK26" s="58"/>
+      <c r="AL26" s="56"/>
+      <c r="AM26" s="57"/>
+      <c r="AN26" s="57"/>
+      <c r="AO26" s="57"/>
+      <c r="AP26" s="57"/>
+      <c r="AQ26" s="57"/>
+      <c r="AR26" s="58"/>
     </row>
     <row r="27" spans="1:44">
-      <c r="A27" s="94"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="98"/>
-      <c r="J27" s="98"/>
-      <c r="K27" s="98"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="98"/>
-      <c r="N27" s="99"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="98"/>
-      <c r="Q27" s="98"/>
-      <c r="R27" s="98"/>
-      <c r="S27" s="98"/>
-      <c r="T27" s="98"/>
-      <c r="U27" s="98"/>
-      <c r="V27" s="98"/>
-      <c r="W27" s="98"/>
-      <c r="X27" s="98"/>
-      <c r="Y27" s="98"/>
-      <c r="Z27" s="98"/>
-      <c r="AA27" s="98"/>
-      <c r="AB27" s="98"/>
-      <c r="AC27" s="98"/>
-      <c r="AD27" s="98"/>
-      <c r="AE27" s="98"/>
-      <c r="AF27" s="98"/>
-      <c r="AG27" s="98"/>
-      <c r="AH27" s="98"/>
-      <c r="AI27" s="98"/>
-      <c r="AJ27" s="98"/>
-      <c r="AK27" s="99"/>
-      <c r="AL27" s="100"/>
-      <c r="AM27" s="98"/>
-      <c r="AN27" s="98"/>
-      <c r="AO27" s="98"/>
-      <c r="AP27" s="98"/>
-      <c r="AQ27" s="98"/>
-      <c r="AR27" s="99"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="57"/>
+      <c r="Q27" s="57"/>
+      <c r="R27" s="57"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="57"/>
+      <c r="U27" s="57"/>
+      <c r="V27" s="57"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+      <c r="AF27" s="57"/>
+      <c r="AG27" s="57"/>
+      <c r="AH27" s="57"/>
+      <c r="AI27" s="57"/>
+      <c r="AJ27" s="57"/>
+      <c r="AK27" s="58"/>
+      <c r="AL27" s="56"/>
+      <c r="AM27" s="57"/>
+      <c r="AN27" s="57"/>
+      <c r="AO27" s="57"/>
+      <c r="AP27" s="57"/>
+      <c r="AQ27" s="57"/>
+      <c r="AR27" s="58"/>
     </row>
     <row r="28" spans="1:44">
-      <c r="A28" s="94"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
-      <c r="G28" s="99"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="98"/>
-      <c r="J28" s="98"/>
-      <c r="K28" s="98"/>
-      <c r="L28" s="98"/>
-      <c r="M28" s="98"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="100"/>
-      <c r="P28" s="98"/>
-      <c r="Q28" s="98"/>
-      <c r="R28" s="98"/>
-      <c r="S28" s="98"/>
-      <c r="T28" s="98"/>
-      <c r="U28" s="98"/>
-      <c r="V28" s="98"/>
-      <c r="W28" s="98"/>
-      <c r="X28" s="98"/>
-      <c r="Y28" s="98"/>
-      <c r="Z28" s="98"/>
-      <c r="AA28" s="98"/>
-      <c r="AB28" s="98"/>
-      <c r="AC28" s="98"/>
-      <c r="AD28" s="98"/>
-      <c r="AE28" s="98"/>
-      <c r="AF28" s="98"/>
-      <c r="AG28" s="98"/>
-      <c r="AH28" s="98"/>
-      <c r="AI28" s="98"/>
-      <c r="AJ28" s="98"/>
-      <c r="AK28" s="99"/>
-      <c r="AL28" s="100"/>
-      <c r="AM28" s="98"/>
-      <c r="AN28" s="98"/>
-      <c r="AO28" s="98"/>
-      <c r="AP28" s="98"/>
-      <c r="AQ28" s="98"/>
-      <c r="AR28" s="99"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="57"/>
+      <c r="Q28" s="57"/>
+      <c r="R28" s="57"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="57"/>
+      <c r="U28" s="57"/>
+      <c r="V28" s="57"/>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+      <c r="AF28" s="57"/>
+      <c r="AG28" s="57"/>
+      <c r="AH28" s="57"/>
+      <c r="AI28" s="57"/>
+      <c r="AJ28" s="57"/>
+      <c r="AK28" s="58"/>
+      <c r="AL28" s="56"/>
+      <c r="AM28" s="57"/>
+      <c r="AN28" s="57"/>
+      <c r="AO28" s="57"/>
+      <c r="AP28" s="57"/>
+      <c r="AQ28" s="57"/>
+      <c r="AR28" s="58"/>
     </row>
     <row r="29" spans="1:44">
-      <c r="A29" s="94"/>
-      <c r="B29" s="95"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="99"/>
-      <c r="H29" s="100"/>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="98"/>
-      <c r="N29" s="99"/>
-      <c r="O29" s="100"/>
-      <c r="P29" s="98"/>
-      <c r="Q29" s="98"/>
-      <c r="R29" s="98"/>
-      <c r="S29" s="98"/>
-      <c r="T29" s="98"/>
-      <c r="U29" s="98"/>
-      <c r="V29" s="98"/>
-      <c r="W29" s="98"/>
-      <c r="X29" s="98"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="98"/>
-      <c r="AA29" s="98"/>
-      <c r="AB29" s="98"/>
-      <c r="AC29" s="98"/>
-      <c r="AD29" s="98"/>
-      <c r="AE29" s="98"/>
-      <c r="AF29" s="98"/>
-      <c r="AG29" s="98"/>
-      <c r="AH29" s="98"/>
-      <c r="AI29" s="98"/>
-      <c r="AJ29" s="98"/>
-      <c r="AK29" s="99"/>
-      <c r="AL29" s="100"/>
-      <c r="AM29" s="98"/>
-      <c r="AN29" s="98"/>
-      <c r="AO29" s="98"/>
-      <c r="AP29" s="98"/>
-      <c r="AQ29" s="98"/>
-      <c r="AR29" s="99"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="57"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="57"/>
+      <c r="Y29" s="57"/>
+      <c r="Z29" s="57"/>
+      <c r="AA29" s="57"/>
+      <c r="AB29" s="57"/>
+      <c r="AC29" s="57"/>
+      <c r="AD29" s="57"/>
+      <c r="AE29" s="57"/>
+      <c r="AF29" s="57"/>
+      <c r="AG29" s="57"/>
+      <c r="AH29" s="57"/>
+      <c r="AI29" s="57"/>
+      <c r="AJ29" s="57"/>
+      <c r="AK29" s="58"/>
+      <c r="AL29" s="56"/>
+      <c r="AM29" s="57"/>
+      <c r="AN29" s="57"/>
+      <c r="AO29" s="57"/>
+      <c r="AP29" s="57"/>
+      <c r="AQ29" s="57"/>
+      <c r="AR29" s="58"/>
     </row>
     <row r="30" spans="1:44">
-      <c r="A30" s="94"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="98"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="98"/>
-      <c r="M30" s="98"/>
-      <c r="N30" s="99"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="98"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="98"/>
-      <c r="T30" s="98"/>
-      <c r="U30" s="98"/>
-      <c r="V30" s="98"/>
-      <c r="W30" s="98"/>
-      <c r="X30" s="98"/>
-      <c r="Y30" s="98"/>
-      <c r="Z30" s="98"/>
-      <c r="AA30" s="98"/>
-      <c r="AB30" s="98"/>
-      <c r="AC30" s="98"/>
-      <c r="AD30" s="98"/>
-      <c r="AE30" s="98"/>
-      <c r="AF30" s="98"/>
-      <c r="AG30" s="98"/>
-      <c r="AH30" s="98"/>
-      <c r="AI30" s="98"/>
-      <c r="AJ30" s="98"/>
-      <c r="AK30" s="99"/>
-      <c r="AL30" s="100"/>
-      <c r="AM30" s="98"/>
-      <c r="AN30" s="98"/>
-      <c r="AO30" s="98"/>
-      <c r="AP30" s="98"/>
-      <c r="AQ30" s="98"/>
-      <c r="AR30" s="99"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="57"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="57"/>
+      <c r="X30" s="57"/>
+      <c r="Y30" s="57"/>
+      <c r="Z30" s="57"/>
+      <c r="AA30" s="57"/>
+      <c r="AB30" s="57"/>
+      <c r="AC30" s="57"/>
+      <c r="AD30" s="57"/>
+      <c r="AE30" s="57"/>
+      <c r="AF30" s="57"/>
+      <c r="AG30" s="57"/>
+      <c r="AH30" s="57"/>
+      <c r="AI30" s="57"/>
+      <c r="AJ30" s="57"/>
+      <c r="AK30" s="58"/>
+      <c r="AL30" s="56"/>
+      <c r="AM30" s="57"/>
+      <c r="AN30" s="57"/>
+      <c r="AO30" s="57"/>
+      <c r="AP30" s="57"/>
+      <c r="AQ30" s="57"/>
+      <c r="AR30" s="58"/>
     </row>
     <row r="31" spans="1:44">
-      <c r="A31" s="94"/>
-      <c r="B31" s="95"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="100"/>
-      <c r="I31" s="98"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="98"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="98"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="98"/>
-      <c r="R31" s="98"/>
-      <c r="S31" s="98"/>
-      <c r="T31" s="98"/>
-      <c r="U31" s="98"/>
-      <c r="V31" s="98"/>
-      <c r="W31" s="98"/>
-      <c r="X31" s="98"/>
-      <c r="Y31" s="98"/>
-      <c r="Z31" s="98"/>
-      <c r="AA31" s="98"/>
-      <c r="AB31" s="98"/>
-      <c r="AC31" s="98"/>
-      <c r="AD31" s="98"/>
-      <c r="AE31" s="98"/>
-      <c r="AF31" s="98"/>
-      <c r="AG31" s="98"/>
-      <c r="AH31" s="98"/>
-      <c r="AI31" s="98"/>
-      <c r="AJ31" s="98"/>
-      <c r="AK31" s="99"/>
-      <c r="AL31" s="100"/>
-      <c r="AM31" s="98"/>
-      <c r="AN31" s="98"/>
-      <c r="AO31" s="98"/>
-      <c r="AP31" s="98"/>
-      <c r="AQ31" s="98"/>
-      <c r="AR31" s="99"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="57"/>
+      <c r="Y31" s="57"/>
+      <c r="Z31" s="57"/>
+      <c r="AA31" s="57"/>
+      <c r="AB31" s="57"/>
+      <c r="AC31" s="57"/>
+      <c r="AD31" s="57"/>
+      <c r="AE31" s="57"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="57"/>
+      <c r="AH31" s="57"/>
+      <c r="AI31" s="57"/>
+      <c r="AJ31" s="57"/>
+      <c r="AK31" s="58"/>
+      <c r="AL31" s="56"/>
+      <c r="AM31" s="57"/>
+      <c r="AN31" s="57"/>
+      <c r="AO31" s="57"/>
+      <c r="AP31" s="57"/>
+      <c r="AQ31" s="57"/>
+      <c r="AR31" s="58"/>
     </row>
     <row r="32" spans="1:44">
-      <c r="A32" s="94"/>
-      <c r="B32" s="95"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
-      <c r="K32" s="98"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="98"/>
-      <c r="N32" s="99"/>
-      <c r="O32" s="100"/>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="98"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="98"/>
-      <c r="T32" s="98"/>
-      <c r="U32" s="98"/>
-      <c r="V32" s="98"/>
-      <c r="W32" s="98"/>
-      <c r="X32" s="98"/>
-      <c r="Y32" s="98"/>
-      <c r="Z32" s="98"/>
-      <c r="AA32" s="98"/>
-      <c r="AB32" s="98"/>
-      <c r="AC32" s="98"/>
-      <c r="AD32" s="98"/>
-      <c r="AE32" s="98"/>
-      <c r="AF32" s="98"/>
-      <c r="AG32" s="98"/>
-      <c r="AH32" s="98"/>
-      <c r="AI32" s="98"/>
-      <c r="AJ32" s="98"/>
-      <c r="AK32" s="99"/>
-      <c r="AL32" s="100"/>
-      <c r="AM32" s="98"/>
-      <c r="AN32" s="98"/>
-      <c r="AO32" s="98"/>
-      <c r="AP32" s="98"/>
-      <c r="AQ32" s="98"/>
-      <c r="AR32" s="99"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="57"/>
+      <c r="Q32" s="57"/>
+      <c r="R32" s="57"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="57"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="57"/>
+      <c r="Y32" s="57"/>
+      <c r="Z32" s="57"/>
+      <c r="AA32" s="57"/>
+      <c r="AB32" s="57"/>
+      <c r="AC32" s="57"/>
+      <c r="AD32" s="57"/>
+      <c r="AE32" s="57"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="57"/>
+      <c r="AH32" s="57"/>
+      <c r="AI32" s="57"/>
+      <c r="AJ32" s="57"/>
+      <c r="AK32" s="58"/>
+      <c r="AL32" s="56"/>
+      <c r="AM32" s="57"/>
+      <c r="AN32" s="57"/>
+      <c r="AO32" s="57"/>
+      <c r="AP32" s="57"/>
+      <c r="AQ32" s="57"/>
+      <c r="AR32" s="58"/>
     </row>
     <row r="33" spans="1:44">
-      <c r="A33" s="94"/>
-      <c r="B33" s="95"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="100"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="100"/>
-      <c r="I33" s="98"/>
-      <c r="J33" s="98"/>
-      <c r="K33" s="98"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="98"/>
-      <c r="N33" s="99"/>
-      <c r="O33" s="100"/>
-      <c r="P33" s="98"/>
-      <c r="Q33" s="98"/>
-      <c r="R33" s="98"/>
-      <c r="S33" s="98"/>
-      <c r="T33" s="98"/>
-      <c r="U33" s="98"/>
-      <c r="V33" s="98"/>
-      <c r="W33" s="98"/>
-      <c r="X33" s="98"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="98"/>
-      <c r="AA33" s="98"/>
-      <c r="AB33" s="98"/>
-      <c r="AC33" s="98"/>
-      <c r="AD33" s="98"/>
-      <c r="AE33" s="98"/>
-      <c r="AF33" s="98"/>
-      <c r="AG33" s="98"/>
-      <c r="AH33" s="98"/>
-      <c r="AI33" s="98"/>
-      <c r="AJ33" s="98"/>
-      <c r="AK33" s="99"/>
-      <c r="AL33" s="100"/>
-      <c r="AM33" s="98"/>
-      <c r="AN33" s="98"/>
-      <c r="AO33" s="98"/>
-      <c r="AP33" s="98"/>
-      <c r="AQ33" s="98"/>
-      <c r="AR33" s="99"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="57"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="57"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="57"/>
+      <c r="Y33" s="57"/>
+      <c r="Z33" s="57"/>
+      <c r="AA33" s="57"/>
+      <c r="AB33" s="57"/>
+      <c r="AC33" s="57"/>
+      <c r="AD33" s="57"/>
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="57"/>
+      <c r="AH33" s="57"/>
+      <c r="AI33" s="57"/>
+      <c r="AJ33" s="57"/>
+      <c r="AK33" s="58"/>
+      <c r="AL33" s="56"/>
+      <c r="AM33" s="57"/>
+      <c r="AN33" s="57"/>
+      <c r="AO33" s="57"/>
+      <c r="AP33" s="57"/>
+      <c r="AQ33" s="57"/>
+      <c r="AR33" s="58"/>
     </row>
     <row r="34" spans="1:44">
-      <c r="A34" s="94"/>
-      <c r="B34" s="95"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="99"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="100"/>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="98"/>
-      <c r="R34" s="98"/>
-      <c r="S34" s="98"/>
-      <c r="T34" s="98"/>
-      <c r="U34" s="98"/>
-      <c r="V34" s="98"/>
-      <c r="W34" s="98"/>
-      <c r="X34" s="98"/>
-      <c r="Y34" s="98"/>
-      <c r="Z34" s="98"/>
-      <c r="AA34" s="98"/>
-      <c r="AB34" s="98"/>
-      <c r="AC34" s="98"/>
-      <c r="AD34" s="98"/>
-      <c r="AE34" s="98"/>
-      <c r="AF34" s="98"/>
-      <c r="AG34" s="98"/>
-      <c r="AH34" s="98"/>
-      <c r="AI34" s="98"/>
-      <c r="AJ34" s="98"/>
-      <c r="AK34" s="99"/>
-      <c r="AL34" s="100"/>
-      <c r="AM34" s="98"/>
-      <c r="AN34" s="98"/>
-      <c r="AO34" s="98"/>
-      <c r="AP34" s="98"/>
-      <c r="AQ34" s="98"/>
-      <c r="AR34" s="99"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="56"/>
+      <c r="P34" s="57"/>
+      <c r="Q34" s="57"/>
+      <c r="R34" s="57"/>
+      <c r="S34" s="57"/>
+      <c r="T34" s="57"/>
+      <c r="U34" s="57"/>
+      <c r="V34" s="57"/>
+      <c r="W34" s="57"/>
+      <c r="X34" s="57"/>
+      <c r="Y34" s="57"/>
+      <c r="Z34" s="57"/>
+      <c r="AA34" s="57"/>
+      <c r="AB34" s="57"/>
+      <c r="AC34" s="57"/>
+      <c r="AD34" s="57"/>
+      <c r="AE34" s="57"/>
+      <c r="AF34" s="57"/>
+      <c r="AG34" s="57"/>
+      <c r="AH34" s="57"/>
+      <c r="AI34" s="57"/>
+      <c r="AJ34" s="57"/>
+      <c r="AK34" s="58"/>
+      <c r="AL34" s="56"/>
+      <c r="AM34" s="57"/>
+      <c r="AN34" s="57"/>
+      <c r="AO34" s="57"/>
+      <c r="AP34" s="57"/>
+      <c r="AQ34" s="57"/>
+      <c r="AR34" s="58"/>
     </row>
     <row r="35" spans="1:44">
-      <c r="A35" s="94"/>
-      <c r="B35" s="95"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="100"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="99"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="98"/>
-      <c r="K35" s="98"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="98"/>
-      <c r="N35" s="99"/>
-      <c r="O35" s="100"/>
-      <c r="P35" s="98"/>
-      <c r="Q35" s="98"/>
-      <c r="R35" s="98"/>
-      <c r="S35" s="98"/>
-      <c r="T35" s="98"/>
-      <c r="U35" s="98"/>
-      <c r="V35" s="98"/>
-      <c r="W35" s="98"/>
-      <c r="X35" s="98"/>
-      <c r="Y35" s="98"/>
-      <c r="Z35" s="98"/>
-      <c r="AA35" s="98"/>
-      <c r="AB35" s="98"/>
-      <c r="AC35" s="98"/>
-      <c r="AD35" s="98"/>
-      <c r="AE35" s="98"/>
-      <c r="AF35" s="98"/>
-      <c r="AG35" s="98"/>
-      <c r="AH35" s="98"/>
-      <c r="AI35" s="98"/>
-      <c r="AJ35" s="98"/>
-      <c r="AK35" s="99"/>
-      <c r="AL35" s="100"/>
-      <c r="AM35" s="98"/>
-      <c r="AN35" s="98"/>
-      <c r="AO35" s="98"/>
-      <c r="AP35" s="98"/>
-      <c r="AQ35" s="98"/>
-      <c r="AR35" s="99"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="56"/>
+      <c r="P35" s="57"/>
+      <c r="Q35" s="57"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="57"/>
+      <c r="V35" s="57"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="57"/>
+      <c r="Y35" s="57"/>
+      <c r="Z35" s="57"/>
+      <c r="AA35" s="57"/>
+      <c r="AB35" s="57"/>
+      <c r="AC35" s="57"/>
+      <c r="AD35" s="57"/>
+      <c r="AE35" s="57"/>
+      <c r="AF35" s="57"/>
+      <c r="AG35" s="57"/>
+      <c r="AH35" s="57"/>
+      <c r="AI35" s="57"/>
+      <c r="AJ35" s="57"/>
+      <c r="AK35" s="58"/>
+      <c r="AL35" s="56"/>
+      <c r="AM35" s="57"/>
+      <c r="AN35" s="57"/>
+      <c r="AO35" s="57"/>
+      <c r="AP35" s="57"/>
+      <c r="AQ35" s="57"/>
+      <c r="AR35" s="58"/>
     </row>
     <row r="36" spans="1:44" ht="11.25" customHeight="1">
-      <c r="A36" s="94"/>
-      <c r="B36" s="95"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="100"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="99"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="98"/>
-      <c r="J36" s="98"/>
-      <c r="K36" s="98"/>
-      <c r="L36" s="98"/>
-      <c r="M36" s="98"/>
-      <c r="N36" s="99"/>
-      <c r="O36" s="100"/>
-      <c r="P36" s="98"/>
-      <c r="Q36" s="98"/>
-      <c r="R36" s="98"/>
-      <c r="S36" s="98"/>
-      <c r="T36" s="98"/>
-      <c r="U36" s="98"/>
-      <c r="V36" s="98"/>
-      <c r="W36" s="98"/>
-      <c r="X36" s="98"/>
-      <c r="Y36" s="98"/>
-      <c r="Z36" s="98"/>
-      <c r="AA36" s="98"/>
-      <c r="AB36" s="98"/>
-      <c r="AC36" s="98"/>
-      <c r="AD36" s="98"/>
-      <c r="AE36" s="98"/>
-      <c r="AF36" s="98"/>
-      <c r="AG36" s="98"/>
-      <c r="AH36" s="98"/>
-      <c r="AI36" s="98"/>
-      <c r="AJ36" s="98"/>
-      <c r="AK36" s="99"/>
-      <c r="AL36" s="100"/>
-      <c r="AM36" s="98"/>
-      <c r="AN36" s="98"/>
-      <c r="AO36" s="98"/>
-      <c r="AP36" s="98"/>
-      <c r="AQ36" s="98"/>
-      <c r="AR36" s="99"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="56"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="57"/>
+      <c r="V36" s="57"/>
+      <c r="W36" s="57"/>
+      <c r="X36" s="57"/>
+      <c r="Y36" s="57"/>
+      <c r="Z36" s="57"/>
+      <c r="AA36" s="57"/>
+      <c r="AB36" s="57"/>
+      <c r="AC36" s="57"/>
+      <c r="AD36" s="57"/>
+      <c r="AE36" s="57"/>
+      <c r="AF36" s="57"/>
+      <c r="AG36" s="57"/>
+      <c r="AH36" s="57"/>
+      <c r="AI36" s="57"/>
+      <c r="AJ36" s="57"/>
+      <c r="AK36" s="58"/>
+      <c r="AL36" s="56"/>
+      <c r="AM36" s="57"/>
+      <c r="AN36" s="57"/>
+      <c r="AO36" s="57"/>
+      <c r="AP36" s="57"/>
+      <c r="AQ36" s="57"/>
+      <c r="AR36" s="58"/>
     </row>
     <row r="37" spans="1:44">
-      <c r="A37" s="94"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="100"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="98"/>
-      <c r="J37" s="98"/>
-      <c r="K37" s="98"/>
-      <c r="L37" s="98"/>
-      <c r="M37" s="98"/>
-      <c r="N37" s="99"/>
-      <c r="O37" s="100"/>
-      <c r="P37" s="98"/>
-      <c r="Q37" s="98"/>
-      <c r="R37" s="98"/>
-      <c r="S37" s="98"/>
-      <c r="T37" s="98"/>
-      <c r="U37" s="98"/>
-      <c r="V37" s="98"/>
-      <c r="W37" s="98"/>
-      <c r="X37" s="98"/>
-      <c r="Y37" s="98"/>
-      <c r="Z37" s="98"/>
-      <c r="AA37" s="98"/>
-      <c r="AB37" s="98"/>
-      <c r="AC37" s="98"/>
-      <c r="AD37" s="98"/>
-      <c r="AE37" s="98"/>
-      <c r="AF37" s="98"/>
-      <c r="AG37" s="98"/>
-      <c r="AH37" s="98"/>
-      <c r="AI37" s="98"/>
-      <c r="AJ37" s="98"/>
-      <c r="AK37" s="99"/>
-      <c r="AL37" s="100"/>
-      <c r="AM37" s="98"/>
-      <c r="AN37" s="98"/>
-      <c r="AO37" s="98"/>
-      <c r="AP37" s="98"/>
-      <c r="AQ37" s="98"/>
-      <c r="AR37" s="99"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="56"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="57"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="57"/>
+      <c r="Y37" s="57"/>
+      <c r="Z37" s="57"/>
+      <c r="AA37" s="57"/>
+      <c r="AB37" s="57"/>
+      <c r="AC37" s="57"/>
+      <c r="AD37" s="57"/>
+      <c r="AE37" s="57"/>
+      <c r="AF37" s="57"/>
+      <c r="AG37" s="57"/>
+      <c r="AH37" s="57"/>
+      <c r="AI37" s="57"/>
+      <c r="AJ37" s="57"/>
+      <c r="AK37" s="58"/>
+      <c r="AL37" s="56"/>
+      <c r="AM37" s="57"/>
+      <c r="AN37" s="57"/>
+      <c r="AO37" s="57"/>
+      <c r="AP37" s="57"/>
+      <c r="AQ37" s="57"/>
+      <c r="AR37" s="58"/>
     </row>
     <row r="38" spans="1:44">
       <c r="S38" s="3"/>
@@ -4214,160 +4216,6 @@
     </row>
   </sheetData>
   <mergeCells count="171">
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="H37:N37"/>
-    <mergeCell ref="O37:AK37"/>
-    <mergeCell ref="AL37:AR37"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AK35"/>
-    <mergeCell ref="AL35:AR35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="H36:N36"/>
-    <mergeCell ref="O36:AK36"/>
-    <mergeCell ref="AL36:AR36"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="O33:AK33"/>
-    <mergeCell ref="AL33:AR33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AK34"/>
-    <mergeCell ref="AL34:AR34"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AK31"/>
-    <mergeCell ref="AL31:AR31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AK32"/>
-    <mergeCell ref="AL32:AR32"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AK29"/>
-    <mergeCell ref="AL29:AR29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AK30"/>
-    <mergeCell ref="AL30:AR30"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="O27:AK27"/>
-    <mergeCell ref="AL27:AR27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AK28"/>
-    <mergeCell ref="AL28:AR28"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AK25"/>
-    <mergeCell ref="AL25:AR25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AK26"/>
-    <mergeCell ref="AL26:AR26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AK23"/>
-    <mergeCell ref="AL23:AR23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AK24"/>
-    <mergeCell ref="AL24:AR24"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AK21"/>
-    <mergeCell ref="AL21:AR21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AK22"/>
-    <mergeCell ref="AL22:AR22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AK19"/>
-    <mergeCell ref="AL19:AR19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AK20"/>
-    <mergeCell ref="AL20:AR20"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AK17"/>
-    <mergeCell ref="AL17:AR17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AK18"/>
-    <mergeCell ref="AL18:AR18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O15:AK15"/>
-    <mergeCell ref="AL15:AR15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O16:AK16"/>
-    <mergeCell ref="AL16:AR16"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AK13"/>
-    <mergeCell ref="AL13:AR13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AK14"/>
-    <mergeCell ref="AL14:AR14"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="O11:AK11"/>
-    <mergeCell ref="AL11:AR11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AK12"/>
-    <mergeCell ref="AL12:AR12"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AK9"/>
-    <mergeCell ref="AL9:AR9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AK10"/>
-    <mergeCell ref="AL10:AR10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="AL7:AR7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:AK8"/>
-    <mergeCell ref="AL8:AR8"/>
     <mergeCell ref="A1:I3"/>
     <mergeCell ref="J1:N1"/>
     <mergeCell ref="O1:X1"/>
@@ -4385,6 +4233,160 @@
     <mergeCell ref="O3:X3"/>
     <mergeCell ref="Y3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="AL7:AR7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:AK8"/>
+    <mergeCell ref="AL8:AR8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AK9"/>
+    <mergeCell ref="AL9:AR9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AK10"/>
+    <mergeCell ref="AL10:AR10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="O11:AK11"/>
+    <mergeCell ref="AL11:AR11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AK12"/>
+    <mergeCell ref="AL12:AR12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AK13"/>
+    <mergeCell ref="AL13:AR13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AK14"/>
+    <mergeCell ref="AL14:AR14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O15:AK15"/>
+    <mergeCell ref="AL15:AR15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:AK16"/>
+    <mergeCell ref="AL16:AR16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AK17"/>
+    <mergeCell ref="AL17:AR17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AK18"/>
+    <mergeCell ref="AL18:AR18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AK19"/>
+    <mergeCell ref="AL19:AR19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AK20"/>
+    <mergeCell ref="AL20:AR20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AK21"/>
+    <mergeCell ref="AL21:AR21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AK22"/>
+    <mergeCell ref="AL22:AR22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AK23"/>
+    <mergeCell ref="AL23:AR23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AK24"/>
+    <mergeCell ref="AL24:AR24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AK25"/>
+    <mergeCell ref="AL25:AR25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AK26"/>
+    <mergeCell ref="AL26:AR26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="O27:AK27"/>
+    <mergeCell ref="AL27:AR27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AK28"/>
+    <mergeCell ref="AL28:AR28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AK29"/>
+    <mergeCell ref="AL29:AR29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AK30"/>
+    <mergeCell ref="AL30:AR30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AK31"/>
+    <mergeCell ref="AL31:AR31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AK32"/>
+    <mergeCell ref="AL32:AR32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="O33:AK33"/>
+    <mergeCell ref="AL33:AR33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AK34"/>
+    <mergeCell ref="AL34:AR34"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="H37:N37"/>
+    <mergeCell ref="O37:AK37"/>
+    <mergeCell ref="AL37:AR37"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AK35"/>
+    <mergeCell ref="AL35:AR35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="H36:N36"/>
+    <mergeCell ref="O36:AK36"/>
+    <mergeCell ref="AL36:AR36"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -4411,57 +4413,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="61" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
       <c r="J1" s="38"/>
       <c r="K1" s="34"/>
       <c r="L1" s="34"/>
       <c r="M1" s="34"/>
       <c r="N1" s="34"/>
       <c r="O1" s="34"/>
-      <c r="P1" s="66" t="s">
+      <c r="P1" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="68"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="83"/>
       <c r="T1" s="33"/>
       <c r="U1" s="33"/>
       <c r="V1" s="34"/>
       <c r="W1" s="34"/>
       <c r="X1" s="34"/>
       <c r="Y1" s="35"/>
-      <c r="Z1" s="102" t="s">
+      <c r="Z1" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="AA1" s="75" t="s">
+      <c r="AA1" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" s="77"/>
+      <c r="AB1" s="92"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="61" t="s">
+      <c r="A2" s="119"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
       <c r="J2" s="38" t="s">
         <v>109</v>
       </c>
@@ -4470,12 +4472,12 @@
       <c r="M2" s="34"/>
       <c r="N2" s="34"/>
       <c r="O2" s="34"/>
-      <c r="P2" s="66" t="s">
+      <c r="P2" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="68"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="83"/>
       <c r="T2" s="39" t="s">
         <v>60</v>
       </c>
@@ -4486,137 +4488,137 @@
       <c r="W2" s="33"/>
       <c r="X2" s="33"/>
       <c r="Y2" s="37"/>
-      <c r="Z2" s="103"/>
-      <c r="AA2" s="78"/>
-      <c r="AB2" s="80"/>
+      <c r="Z2" s="134"/>
+      <c r="AA2" s="93"/>
+      <c r="AB2" s="95"/>
     </row>
     <row r="3" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="61" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="38" t="s">
-        <v>124</v>
+      <c r="G3" s="82"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="52" t="s">
+        <v>158</v>
       </c>
       <c r="K3" s="34"/>
       <c r="L3" s="34"/>
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
       <c r="O3" s="34"/>
-      <c r="P3" s="66" t="s">
+      <c r="P3" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="68"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="83"/>
       <c r="T3" s="33"/>
       <c r="U3" s="33"/>
       <c r="V3" s="36"/>
       <c r="W3" s="33"/>
       <c r="X3" s="33"/>
       <c r="Y3" s="37"/>
-      <c r="Z3" s="104"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="83"/>
+      <c r="Z3" s="135"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="98"/>
     </row>
     <row r="4" spans="1:40" ht="15" customHeight="1" thickTop="1"/>
     <row r="5" spans="1:40" ht="15" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="128" t="s">
+      <c r="B5" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="129"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="128" t="s">
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="L5" s="129"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="133" t="s">
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="P5" s="120" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q5" s="122" t="s">
+      <c r="P5" s="131" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q5" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="R5" s="124"/>
-      <c r="S5" s="122" t="s">
+      <c r="R5" s="105"/>
+      <c r="S5" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="T5" s="123"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="123"/>
-      <c r="W5" s="123"/>
-      <c r="X5" s="123"/>
-      <c r="Y5" s="123"/>
-      <c r="Z5" s="123"/>
-      <c r="AA5" s="123"/>
-      <c r="AB5" s="124"/>
+      <c r="T5" s="104"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="104"/>
+      <c r="W5" s="104"/>
+      <c r="X5" s="104"/>
+      <c r="Y5" s="104"/>
+      <c r="Z5" s="104"/>
+      <c r="AA5" s="104"/>
+      <c r="AB5" s="105"/>
       <c r="AD5" s="2" t="str">
         <f>"-- " &amp; J2</f>
         <v>-- 銘柄基本情報</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="132"/>
-      <c r="B6" s="114" t="s">
+      <c r="A6" s="113"/>
+      <c r="B6" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117" t="s">
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="118" t="s">
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="L6" s="119"/>
+      <c r="L6" s="130"/>
       <c r="M6" s="18" t="s">
         <v>99</v>
       </c>
       <c r="N6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="O6" s="134"/>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="125"/>
-      <c r="R6" s="127"/>
-      <c r="S6" s="125"/>
-      <c r="T6" s="126"/>
-      <c r="U6" s="126"/>
-      <c r="V6" s="126"/>
-      <c r="W6" s="126"/>
-      <c r="X6" s="126"/>
-      <c r="Y6" s="126"/>
-      <c r="Z6" s="126"/>
-      <c r="AA6" s="126"/>
-      <c r="AB6" s="127"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="132"/>
+      <c r="Q6" s="106"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="106"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="107"/>
+      <c r="W6" s="107"/>
+      <c r="X6" s="107"/>
+      <c r="Y6" s="107"/>
+      <c r="Z6" s="107"/>
+      <c r="AA6" s="107"/>
+      <c r="AB6" s="108"/>
       <c r="AD6" s="2" t="str">
         <f>"CREATE TABLE " &amp; J3 &amp;" ("</f>
-        <v>CREATE TABLE company_statistics (</v>
+        <v>CREATE TABLE equity_statistics (</v>
       </c>
     </row>
     <row r="7" spans="1:40" ht="15" customHeight="1" thickTop="1">
@@ -4637,7 +4639,7 @@
       <c r="I7" s="25"/>
       <c r="J7" s="26"/>
       <c r="K7" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L7" s="23"/>
       <c r="M7" s="27">
@@ -4693,7 +4695,7 @@
       <c r="I8" s="25"/>
       <c r="J8" s="26"/>
       <c r="K8" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L8" s="23"/>
       <c r="M8" s="29">
@@ -4745,7 +4747,7 @@
       <c r="I9" s="25"/>
       <c r="J9" s="26"/>
       <c r="K9" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L9" s="23"/>
       <c r="M9" s="29">
@@ -4797,7 +4799,7 @@
       <c r="I10" s="25"/>
       <c r="J10" s="26"/>
       <c r="K10" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L10" s="23"/>
       <c r="M10" s="40">
@@ -4851,7 +4853,7 @@
       <c r="I11" s="25"/>
       <c r="J11" s="26"/>
       <c r="K11" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L11" s="23"/>
       <c r="M11" s="40">
@@ -4905,7 +4907,7 @@
       <c r="I12" s="25"/>
       <c r="J12" s="26"/>
       <c r="K12" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L12" s="23"/>
       <c r="M12" s="29"/>
@@ -4955,7 +4957,7 @@
       <c r="I13" s="25"/>
       <c r="J13" s="26"/>
       <c r="K13" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L13" s="23"/>
       <c r="M13" s="29"/>
@@ -4998,14 +5000,14 @@
       <c r="D14" s="25"/>
       <c r="E14" s="26"/>
       <c r="F14" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="I14" s="25"/>
       <c r="J14" s="26"/>
       <c r="K14" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L14" s="44"/>
       <c r="M14" s="29"/>
@@ -5057,7 +5059,7 @@
       <c r="I15" s="25"/>
       <c r="J15" s="26"/>
       <c r="K15" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L15" s="23"/>
       <c r="M15" s="40">
@@ -5104,14 +5106,14 @@
       <c r="D16" s="25"/>
       <c r="E16" s="26"/>
       <c r="F16" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
       <c r="J16" s="26"/>
       <c r="K16" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="29"/>
@@ -5163,7 +5165,7 @@
       <c r="I17" s="25"/>
       <c r="J17" s="26"/>
       <c r="K17" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="29"/>
@@ -5208,14 +5210,14 @@
       <c r="D18" s="25"/>
       <c r="E18" s="26"/>
       <c r="F18" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="I18" s="25"/>
       <c r="J18" s="26"/>
       <c r="K18" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="29"/>
@@ -5254,7 +5256,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -5267,7 +5269,7 @@
       <c r="I19" s="25"/>
       <c r="J19" s="26"/>
       <c r="K19" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="29"/>
@@ -5306,7 +5308,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -5319,7 +5321,7 @@
       <c r="I20" s="25"/>
       <c r="J20" s="26"/>
       <c r="K20" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="29"/>
@@ -5358,20 +5360,20 @@
         <v>28</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
       <c r="E21" s="26"/>
       <c r="F21" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="I21" s="25"/>
       <c r="J21" s="26"/>
       <c r="K21" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="29"/>
@@ -5408,20 +5410,20 @@
         <v>11</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
       <c r="E22" s="26"/>
       <c r="F22" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
       <c r="J22" s="26"/>
       <c r="K22" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L22" s="23"/>
       <c r="M22" s="29"/>
@@ -5464,14 +5466,14 @@
       <c r="D23" s="25"/>
       <c r="E23" s="26"/>
       <c r="F23" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="I23" s="25"/>
       <c r="J23" s="26"/>
       <c r="K23" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L23" s="44"/>
       <c r="M23" s="29"/>
@@ -5481,7 +5483,7 @@
       <c r="Q23" s="24"/>
       <c r="R23" s="23"/>
       <c r="S23" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T23" s="15"/>
       <c r="U23" s="20"/>
@@ -5510,7 +5512,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -5523,7 +5525,7 @@
       <c r="I24" s="25"/>
       <c r="J24" s="26"/>
       <c r="K24" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L24" s="44"/>
       <c r="M24" s="29"/>
@@ -5533,7 +5535,7 @@
       <c r="Q24" s="24"/>
       <c r="R24" s="23"/>
       <c r="S24" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T24" s="15"/>
       <c r="U24" s="20"/>
@@ -5562,20 +5564,20 @@
         <v>18</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
       <c r="E25" s="26"/>
       <c r="F25" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
       <c r="J25" s="26"/>
       <c r="K25" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L25" s="44"/>
       <c r="M25" s="29"/>
@@ -5585,7 +5587,7 @@
       <c r="Q25" s="24"/>
       <c r="R25" s="23"/>
       <c r="S25" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="T25" s="15"/>
       <c r="U25" s="20"/>
@@ -5614,20 +5616,20 @@
         <v>19</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
       <c r="E26" s="26"/>
       <c r="F26" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
       <c r="J26" s="26"/>
       <c r="K26" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L26" s="44"/>
       <c r="M26" s="29"/>
@@ -5637,7 +5639,7 @@
       <c r="Q26" s="24"/>
       <c r="R26" s="23"/>
       <c r="S26" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T26" s="15"/>
       <c r="U26" s="20"/>
@@ -5666,7 +5668,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -5679,7 +5681,7 @@
       <c r="I27" s="25"/>
       <c r="J27" s="26"/>
       <c r="K27" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L27" s="44"/>
       <c r="M27" s="29"/>
@@ -5716,7 +5718,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -5729,7 +5731,7 @@
       <c r="I28" s="25"/>
       <c r="J28" s="26"/>
       <c r="K28" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L28" s="44"/>
       <c r="M28" s="29"/>
@@ -5768,7 +5770,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -5781,7 +5783,7 @@
       <c r="I29" s="25"/>
       <c r="J29" s="26"/>
       <c r="K29" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L29" s="44"/>
       <c r="M29" s="29"/>
@@ -5820,7 +5822,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -5833,7 +5835,7 @@
       <c r="I30" s="25"/>
       <c r="J30" s="26"/>
       <c r="K30" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L30" s="44"/>
       <c r="M30" s="29"/>
@@ -5885,7 +5887,7 @@
       <c r="I31" s="25"/>
       <c r="J31" s="26"/>
       <c r="K31" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L31" s="44"/>
       <c r="M31" s="29"/>
@@ -5930,14 +5932,14 @@
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
       <c r="F32" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="J32" s="26"/>
       <c r="K32" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L32" s="44"/>
       <c r="M32" s="29"/>
@@ -5947,12 +5949,12 @@
       <c r="Q32" s="24"/>
       <c r="R32" s="23"/>
       <c r="S32" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T32" s="15"/>
       <c r="U32" s="20"/>
       <c r="V32" s="48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W32" s="49"/>
       <c r="X32" s="48"/>
@@ -5991,7 +5993,7 @@
       <c r="I33" s="25"/>
       <c r="J33" s="26"/>
       <c r="K33" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33" s="44"/>
       <c r="M33" s="29"/>
@@ -6001,7 +6003,7 @@
       <c r="Q33" s="24"/>
       <c r="R33" s="23"/>
       <c r="S33" s="43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T33" s="45"/>
       <c r="U33" s="46"/>
@@ -6036,14 +6038,14 @@
       <c r="D34" s="25"/>
       <c r="E34" s="26"/>
       <c r="F34" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G34" s="25"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="J34" s="26"/>
       <c r="K34" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L34" s="44"/>
       <c r="M34" s="29"/>
@@ -6053,7 +6055,7 @@
       <c r="Q34" s="24"/>
       <c r="R34" s="23"/>
       <c r="S34" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T34" s="15"/>
       <c r="U34" s="20"/>
@@ -6082,7 +6084,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -6095,7 +6097,7 @@
       <c r="I35" s="25"/>
       <c r="J35" s="26"/>
       <c r="K35" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L35" s="44"/>
       <c r="M35" s="29"/>
@@ -6145,7 +6147,7 @@
       <c r="I36" s="25"/>
       <c r="J36" s="26"/>
       <c r="K36" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L36" s="23"/>
       <c r="M36" s="29"/>
@@ -6195,7 +6197,7 @@
       <c r="I37" s="25"/>
       <c r="J37" s="26"/>
       <c r="K37" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L37" s="23"/>
       <c r="M37" s="29"/>
@@ -6232,20 +6234,20 @@
         <v>39</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="26"/>
       <c r="F38" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G38" s="25"/>
       <c r="H38" s="25"/>
       <c r="I38" s="25"/>
       <c r="J38" s="26"/>
       <c r="K38" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L38" s="23"/>
       <c r="M38" s="29"/>
@@ -6295,7 +6297,7 @@
       <c r="I39" s="25"/>
       <c r="J39" s="26"/>
       <c r="K39" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L39" s="23"/>
       <c r="M39" s="29"/>
@@ -6345,7 +6347,7 @@
       <c r="I40" s="25"/>
       <c r="J40" s="26"/>
       <c r="K40" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L40" s="23"/>
       <c r="M40" s="29"/>
@@ -6395,7 +6397,7 @@
       <c r="I41" s="25"/>
       <c r="J41" s="26"/>
       <c r="K41" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L41" s="23"/>
       <c r="M41" s="29"/>
@@ -6445,7 +6447,7 @@
       <c r="I42" s="25"/>
       <c r="J42" s="26"/>
       <c r="K42" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L42" s="23"/>
       <c r="M42" s="29"/>
@@ -6495,7 +6497,7 @@
       <c r="I43" s="25"/>
       <c r="J43" s="26"/>
       <c r="K43" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L43" s="23"/>
       <c r="M43" s="29"/>
@@ -6545,7 +6547,7 @@
       <c r="I44" s="25"/>
       <c r="J44" s="26"/>
       <c r="K44" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L44" s="23"/>
       <c r="M44" s="29"/>
@@ -6595,7 +6597,7 @@
       <c r="I45" s="25"/>
       <c r="J45" s="26"/>
       <c r="K45" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L45" s="23"/>
       <c r="M45" s="29"/>
@@ -6645,7 +6647,7 @@
       <c r="I46" s="25"/>
       <c r="J46" s="26"/>
       <c r="K46" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L46" s="23"/>
       <c r="M46" s="29">
@@ -6697,7 +6699,7 @@
       <c r="I47" s="25"/>
       <c r="J47" s="26"/>
       <c r="K47" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L47" s="23"/>
       <c r="M47" s="29">
@@ -6749,7 +6751,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="26"/>
       <c r="K48" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L48" s="23"/>
       <c r="M48" s="29">
@@ -6801,7 +6803,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="26"/>
       <c r="K49" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L49" s="23"/>
       <c r="M49" s="29">
@@ -6853,7 +6855,7 @@
       <c r="I50" s="25"/>
       <c r="J50" s="26"/>
       <c r="K50" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L50" s="23"/>
       <c r="M50" s="29">
@@ -6905,7 +6907,7 @@
       <c r="I51" s="25"/>
       <c r="J51" s="26"/>
       <c r="K51" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L51" s="23"/>
       <c r="M51" s="29">
@@ -6957,7 +6959,7 @@
       <c r="I52" s="25"/>
       <c r="J52" s="26"/>
       <c r="K52" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L52" s="23"/>
       <c r="M52" s="29"/>
@@ -7007,7 +7009,7 @@
       <c r="I53" s="25"/>
       <c r="J53" s="26"/>
       <c r="K53" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L53" s="23"/>
       <c r="M53" s="29">
@@ -7059,7 +7061,7 @@
       <c r="I54" s="25"/>
       <c r="J54" s="26"/>
       <c r="K54" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L54" s="23"/>
       <c r="M54" s="29">
@@ -7435,17 +7437,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="S5:AB6"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="Q5:R6"/>
-    <mergeCell ref="A1:E3"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="P5:P6"/>
     <mergeCell ref="AA1:AB3"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="P2:S2"/>
@@ -7454,6 +7445,17 @@
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="Z1:Z3"/>
+    <mergeCell ref="A1:E3"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="S5:AB6"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="Q5:R6"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -7482,57 +7484,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="61" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
       <c r="J1" s="38"/>
       <c r="K1" s="34"/>
       <c r="L1" s="34"/>
       <c r="M1" s="34"/>
       <c r="N1" s="34"/>
       <c r="O1" s="34"/>
-      <c r="P1" s="66" t="s">
+      <c r="P1" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="68"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="83"/>
       <c r="T1" s="33"/>
       <c r="U1" s="33"/>
       <c r="V1" s="34"/>
       <c r="W1" s="34"/>
       <c r="X1" s="34"/>
       <c r="Y1" s="35"/>
-      <c r="Z1" s="102" t="s">
+      <c r="Z1" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="AA1" s="75" t="s">
+      <c r="AA1" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" s="77"/>
+      <c r="AB1" s="92"/>
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="61" t="s">
+      <c r="A2" s="119"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
       <c r="J2" s="38" t="s">
         <v>107</v>
       </c>
@@ -7541,12 +7543,12 @@
       <c r="M2" s="34"/>
       <c r="N2" s="34"/>
       <c r="O2" s="34"/>
-      <c r="P2" s="66" t="s">
+      <c r="P2" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="68"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="83"/>
       <c r="T2" s="39" t="s">
         <v>60</v>
       </c>
@@ -7557,22 +7559,22 @@
       <c r="W2" s="33"/>
       <c r="X2" s="33"/>
       <c r="Y2" s="37"/>
-      <c r="Z2" s="103"/>
-      <c r="AA2" s="78"/>
-      <c r="AB2" s="80"/>
+      <c r="Z2" s="134"/>
+      <c r="AA2" s="93"/>
+      <c r="AB2" s="95"/>
     </row>
     <row r="3" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="61" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
       <c r="J3" s="38" t="s">
         <v>106</v>
       </c>
@@ -7581,110 +7583,110 @@
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
       <c r="O3" s="34"/>
-      <c r="P3" s="66" t="s">
+      <c r="P3" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="68"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="83"/>
       <c r="T3" s="33"/>
       <c r="U3" s="33"/>
       <c r="V3" s="36"/>
       <c r="W3" s="33"/>
       <c r="X3" s="33"/>
       <c r="Y3" s="37"/>
-      <c r="Z3" s="104"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="83"/>
+      <c r="Z3" s="135"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="98"/>
     </row>
     <row r="4" spans="1:40" ht="15" customHeight="1" thickTop="1"/>
     <row r="5" spans="1:40" ht="15" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="128" t="s">
+      <c r="B5" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="129"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="128" t="s">
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="L5" s="129"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="133" t="s">
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="P5" s="133" t="s">
+      <c r="P5" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="Q5" s="122" t="s">
+      <c r="Q5" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="R5" s="124"/>
-      <c r="S5" s="122" t="s">
+      <c r="R5" s="105"/>
+      <c r="S5" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="T5" s="123"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="123"/>
-      <c r="W5" s="123"/>
-      <c r="X5" s="123"/>
-      <c r="Y5" s="123"/>
-      <c r="Z5" s="123"/>
-      <c r="AA5" s="123"/>
-      <c r="AB5" s="124"/>
+      <c r="T5" s="104"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="104"/>
+      <c r="W5" s="104"/>
+      <c r="X5" s="104"/>
+      <c r="Y5" s="104"/>
+      <c r="Z5" s="104"/>
+      <c r="AA5" s="104"/>
+      <c r="AB5" s="105"/>
       <c r="AD5" s="2" t="str">
         <f>"-- " &amp; J2</f>
         <v>-- 上場状況</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="132"/>
-      <c r="B6" s="114" t="s">
+      <c r="A6" s="113"/>
+      <c r="B6" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117" t="s">
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="118" t="s">
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="L6" s="119"/>
+      <c r="L6" s="130"/>
       <c r="M6" s="18" t="s">
         <v>99</v>
       </c>
       <c r="N6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="O6" s="134"/>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="125"/>
-      <c r="R6" s="127"/>
-      <c r="S6" s="125"/>
-      <c r="T6" s="126"/>
-      <c r="U6" s="126"/>
-      <c r="V6" s="126"/>
-      <c r="W6" s="126"/>
-      <c r="X6" s="126"/>
-      <c r="Y6" s="126"/>
-      <c r="Z6" s="126"/>
-      <c r="AA6" s="126"/>
-      <c r="AB6" s="127"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="106"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="106"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="107"/>
+      <c r="W6" s="107"/>
+      <c r="X6" s="107"/>
+      <c r="Y6" s="107"/>
+      <c r="Z6" s="107"/>
+      <c r="AA6" s="107"/>
+      <c r="AB6" s="108"/>
       <c r="AD6" s="2" t="str">
         <f>"CREATE TABLE " &amp; J3 &amp;" ("</f>
         <v>CREATE TABLE ListingStatus (</v>
@@ -8318,6 +8320,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:E3"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="Z1:Z3"/>
+    <mergeCell ref="AA1:AB3"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="P3:S3"/>
     <mergeCell ref="S5:AB6"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="F6:J6"/>
@@ -8328,15 +8339,6 @@
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q5:R6"/>
-    <mergeCell ref="A1:E3"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="Z1:Z3"/>
-    <mergeCell ref="AA1:AB3"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="P3:S3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
